--- a/frontend/Premium Final Submission Form (Responses).xlsx
+++ b/frontend/Premium Final Submission Form (Responses).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Personal\internship_portal\frontend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B1BCED5-DF0E-4333-A5FF-B4E65F35039D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53B5113E-D5DE-4734-BBF6-FE23111A88DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{C47EE7DD-172B-4A1B-B9E4-8FA1669923F8}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="57">
   <si>
     <t xml:space="preserve">Full Name </t>
   </si>
@@ -188,6 +188,9 @@
   </si>
   <si>
     <t>Completed</t>
+  </si>
+  <si>
+    <t>M26IP191</t>
   </si>
 </sst>
 </file>
@@ -511,7 +514,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -641,6 +644,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -686,7 +700,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -694,13 +708,10 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1058,7 +1069,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EC2C977-6593-425B-AEB9-E3A7F18DC4A2}">
-  <dimension ref="B1:AB15"/>
+  <dimension ref="B1:AB16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.26953125" customWidth="1"/>
@@ -1088,292 +1099,313 @@
       <c r="F1" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>54</v>
       </c>
       <c r="AB1" s="1"/>
     </row>
     <row r="2" spans="2:28" x14ac:dyDescent="0.35">
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="3" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="3" spans="2:28" x14ac:dyDescent="0.35">
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="3" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="4" spans="2:28" x14ac:dyDescent="0.35">
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="3" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="5" spans="2:28" x14ac:dyDescent="0.35">
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="G5" s="3" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="6" spans="2:28" x14ac:dyDescent="0.35">
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="G6" s="3" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="7" spans="2:28" x14ac:dyDescent="0.35">
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="G7" s="3" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="8" spans="2:28" x14ac:dyDescent="0.35">
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="G8" s="3" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="9" spans="2:28" x14ac:dyDescent="0.35">
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="G9" s="5" t="s">
+      <c r="G9" s="3" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="10" spans="2:28" x14ac:dyDescent="0.35">
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="G10" s="5" t="s">
+      <c r="G10" s="3" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="11" spans="2:28" x14ac:dyDescent="0.35">
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="G11" s="5" t="s">
+      <c r="G11" s="3" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="12" spans="2:28" x14ac:dyDescent="0.35">
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="G12" s="5" t="s">
+      <c r="G12" s="3" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="13" spans="2:28" x14ac:dyDescent="0.35">
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="F13" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="G13" s="5" t="s">
+      <c r="G13" s="3" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="14" spans="2:28" x14ac:dyDescent="0.35">
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F14" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="G14" s="5" t="s">
+      <c r="G14" s="3" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="15" spans="2:28" x14ac:dyDescent="0.35">
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="F15" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="G15" s="5" t="s">
+      <c r="G15" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="16" spans="2:28" x14ac:dyDescent="0.35">
+      <c r="B16" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>55</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/frontend/Premium Final Submission Form (Responses).xlsx
+++ b/frontend/Premium Final Submission Form (Responses).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Personal\internship_portal\frontend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53B5113E-D5DE-4734-BBF6-FE23111A88DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3F169E9-946A-472A-9683-7B4D9F533E41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{C47EE7DD-172B-4A1B-B9E4-8FA1669923F8}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="61">
   <si>
     <t xml:space="preserve">Full Name </t>
   </si>
@@ -191,6 +191,18 @@
   </si>
   <si>
     <t>M26IP191</t>
+  </si>
+  <si>
+    <t>Joshua Samuel D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M26IP289 </t>
+  </si>
+  <si>
+    <t>26T-C-CC</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Cloud Computing Fundamentals</t>
   </si>
 </sst>
 </file>
@@ -514,7 +526,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -644,17 +656,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -700,7 +701,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -711,8 +712,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1069,7 +1073,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EC2C977-6593-425B-AEB9-E3A7F18DC4A2}">
-  <dimension ref="B1:AB16"/>
+  <dimension ref="B1:AB17"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.26953125" customWidth="1"/>
@@ -1385,10 +1389,10 @@
       </c>
     </row>
     <row r="16" spans="2:28" x14ac:dyDescent="0.35">
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="3" t="s">
         <v>56</v>
       </c>
       <c r="D16" s="3" t="s">
@@ -1401,6 +1405,26 @@
         <v>53</v>
       </c>
       <c r="G16" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B17" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G17" s="3" t="s">
         <v>55</v>
       </c>
     </row>

--- a/frontend/Premium Final Submission Form (Responses).xlsx
+++ b/frontend/Premium Final Submission Form (Responses).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Personal\internship_portal\frontend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3F169E9-946A-472A-9683-7B4D9F533E41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7E307F4-D9BB-449D-950D-41B691FDB653}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{C47EE7DD-172B-4A1B-B9E4-8FA1669923F8}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="65">
   <si>
     <t xml:space="preserve">Full Name </t>
   </si>
@@ -203,6 +203,18 @@
   </si>
   <si>
     <t xml:space="preserve"> Cloud Computing Fundamentals</t>
+  </si>
+  <si>
+    <t>Jashwanth V</t>
+  </si>
+  <si>
+    <t>M26IP216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Digital Content Creation </t>
+  </si>
+  <si>
+    <t>26NT-G-DCC</t>
   </si>
 </sst>
 </file>
@@ -712,11 +724,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1073,7 +1085,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EC2C977-6593-425B-AEB9-E3A7F18DC4A2}">
-  <dimension ref="B1:AB17"/>
+  <dimension ref="B1:AB18"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.26953125" customWidth="1"/>
@@ -1409,22 +1421,42 @@
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="E17" s="4" t="s">
         <v>59</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>53</v>
       </c>
       <c r="G17" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B18" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G18" s="3" t="s">
         <v>55</v>
       </c>
     </row>

--- a/frontend/Premium Final Submission Form (Responses).xlsx
+++ b/frontend/Premium Final Submission Form (Responses).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Personal\internship_portal\frontend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7E307F4-D9BB-449D-950D-41B691FDB653}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5DDADE4-7A2F-44F7-AAC9-2A2D67274853}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{C47EE7DD-172B-4A1B-B9E4-8FA1669923F8}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="108">
   <si>
     <t xml:space="preserve">Full Name </t>
   </si>
@@ -215,6 +215,135 @@
   </si>
   <si>
     <t>26NT-G-DCC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BEULAH .C </t>
+  </si>
+  <si>
+    <t>SHANNON T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SHAIK MUNWAAR </t>
+  </si>
+  <si>
+    <t>Bavadhashini S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pavitra kr </t>
+  </si>
+  <si>
+    <t xml:space="preserve">P.SANJAY KUMARAN </t>
+  </si>
+  <si>
+    <t>M.SUBHASHINI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Varsha </t>
+  </si>
+  <si>
+    <t>Deepikha K</t>
+  </si>
+  <si>
+    <t>Alagiya surya M</t>
+  </si>
+  <si>
+    <t>Ghanisha J</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kommineni manvitha chowdary </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kishore P </t>
+  </si>
+  <si>
+    <t>M26IP132</t>
+  </si>
+  <si>
+    <t>M26IP077</t>
+  </si>
+  <si>
+    <t>M26IP152</t>
+  </si>
+  <si>
+    <t>M26IP006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M26IP088 </t>
+  </si>
+  <si>
+    <t>M26IP127</t>
+  </si>
+  <si>
+    <t>M26IP109</t>
+  </si>
+  <si>
+    <t>M26IP082</t>
+  </si>
+  <si>
+    <t>M26IP131</t>
+  </si>
+  <si>
+    <t>M26IP130</t>
+  </si>
+  <si>
+    <t>M26IP133</t>
+  </si>
+  <si>
+    <t>M26IP168</t>
+  </si>
+  <si>
+    <t>M26IP001</t>
+  </si>
+  <si>
+    <t>Python programming</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project management fundamentals </t>
+  </si>
+  <si>
+    <t>Sensor Technology Fundamentals</t>
+  </si>
+  <si>
+    <t>introduction to machine learning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project management Fundamentals </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Web development fundamentals </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Tools &amp; Prompt Engineering </t>
+  </si>
+  <si>
+    <t>WEB DEVELOPMENT AND FUNDAMENTALS</t>
+  </si>
+  <si>
+    <t>Content Writing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Web developement fundamental </t>
+  </si>
+  <si>
+    <t>26NT-B-CW</t>
+  </si>
+  <si>
+    <t>26NT D PM</t>
+  </si>
+  <si>
+    <t>26T-E-SEN</t>
+  </si>
+  <si>
+    <t>26NT-D-PM</t>
+  </si>
+  <si>
+    <t>26T-C-AI</t>
+  </si>
+  <si>
+    <t>Elite</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 26T-A-WD</t>
   </si>
 </sst>
 </file>
@@ -357,7 +486,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -535,6 +664,18 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8F9FA"/>
+        <bgColor rgb="FFF8F9FA"/>
       </patternFill>
     </fill>
   </fills>
@@ -713,7 +854,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -726,6 +867,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1085,7 +1232,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EC2C977-6593-425B-AEB9-E3A7F18DC4A2}">
-  <dimension ref="B1:AB18"/>
+  <dimension ref="B1:AB34"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.26953125" customWidth="1"/>
@@ -1441,22 +1588,302 @@
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D18" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E18" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>53</v>
       </c>
       <c r="G18" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B21" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B22" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B23" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B24" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B25" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B26" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B27" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B28" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="G28" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B29" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B30" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F30" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="G30" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B31" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="G31" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B32" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F32" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="G32" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B33" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="G33" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B34" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="G34" s="7" t="s">
         <v>55</v>
       </c>
     </row>

--- a/frontend/Premium Final Submission Form (Responses).xlsx
+++ b/frontend/Premium Final Submission Form (Responses).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Personal\internship_portal\frontend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5DDADE4-7A2F-44F7-AAC9-2A2D67274853}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0F32F3A-F8DE-49A8-BC5D-56FF3933F929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{C47EE7DD-172B-4A1B-B9E4-8FA1669923F8}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="175">
   <si>
     <t xml:space="preserve">Full Name </t>
   </si>
@@ -344,13 +344,214 @@
   </si>
   <si>
     <t xml:space="preserve"> 26T-A-WD</t>
+  </si>
+  <si>
+    <t>kavya ramadoss</t>
+  </si>
+  <si>
+    <t>S.K.Hariaharan</t>
+  </si>
+  <si>
+    <t>J DIPTO JAISON</t>
+  </si>
+  <si>
+    <t>Akash kumar V</t>
+  </si>
+  <si>
+    <t>S JEGATHISAN</t>
+  </si>
+  <si>
+    <t>Vishva.M</t>
+  </si>
+  <si>
+    <t>Harthe.R</t>
+  </si>
+  <si>
+    <t>Y. BESCHI ANTO</t>
+  </si>
+  <si>
+    <t>Prasanna.K</t>
+  </si>
+  <si>
+    <t>YOGESH KUMAR M</t>
+  </si>
+  <si>
+    <t>Girishkumar M</t>
+  </si>
+  <si>
+    <t>M26IP141</t>
+  </si>
+  <si>
+    <t>M26IP134</t>
+  </si>
+  <si>
+    <t>M26IP139</t>
+  </si>
+  <si>
+    <t>ID:M26IP281</t>
+  </si>
+  <si>
+    <t>M261P199</t>
+  </si>
+  <si>
+    <t>M26IP078</t>
+  </si>
+  <si>
+    <t>M26IP116</t>
+  </si>
+  <si>
+    <t>M26IP007</t>
+  </si>
+  <si>
+    <t>M26IP008</t>
+  </si>
+  <si>
+    <t>M26IP279</t>
+  </si>
+  <si>
+    <t>M26IP003</t>
+  </si>
+  <si>
+    <t>Web development fundamentals</t>
+  </si>
+  <si>
+    <t>Web development fundam</t>
+  </si>
+  <si>
+    <t>Frontend development (HTML &amp; CSS)</t>
+  </si>
+  <si>
+    <t>Medical device fundamentals</t>
+  </si>
+  <si>
+    <t>Entrepreneurship Fundamentals</t>
+  </si>
+  <si>
+    <t>Frontend development</t>
+  </si>
+  <si>
+    <t>26T-J-MD</t>
+  </si>
+  <si>
+    <t>26NT-C-ENT</t>
+  </si>
+  <si>
+    <t>N. ARUN KUMAR</t>
+  </si>
+  <si>
+    <t>KARTHIKEYAN E</t>
+  </si>
+  <si>
+    <t>Lourdu Flavin Romaro B</t>
+  </si>
+  <si>
+    <t>S. Vyash</t>
+  </si>
+  <si>
+    <t>A.Vignesh</t>
+  </si>
+  <si>
+    <t>J.Priyadharshini</t>
+  </si>
+  <si>
+    <t>A. Krishnamoorthy</t>
+  </si>
+  <si>
+    <t>Birundha C</t>
+  </si>
+  <si>
+    <t>KISHORE M</t>
+  </si>
+  <si>
+    <t>KABILAN.M</t>
+  </si>
+  <si>
+    <t>Krishnaraj M</t>
+  </si>
+  <si>
+    <t>Logeshwaran S</t>
+  </si>
+  <si>
+    <t>Syed Saifuddin</t>
+  </si>
+  <si>
+    <t>Santhosh. D</t>
+  </si>
+  <si>
+    <t>Dharsan</t>
+  </si>
+  <si>
+    <t>M26IP275</t>
+  </si>
+  <si>
+    <t>M26IP80</t>
+  </si>
+  <si>
+    <t>M26IP269</t>
+  </si>
+  <si>
+    <t>M26IP268</t>
+  </si>
+  <si>
+    <t>M26IP283</t>
+  </si>
+  <si>
+    <t>M26IP273</t>
+  </si>
+  <si>
+    <t>M26IP274</t>
+  </si>
+  <si>
+    <t>M26IP289</t>
+  </si>
+  <si>
+    <t>M26IP290</t>
+  </si>
+  <si>
+    <t>M26IP292</t>
+  </si>
+  <si>
+    <t>M26IP294</t>
+  </si>
+  <si>
+    <t>M26IP271</t>
+  </si>
+  <si>
+    <t>M26IP282</t>
+  </si>
+  <si>
+    <t>M26IP291</t>
+  </si>
+  <si>
+    <t>M26IP266</t>
+  </si>
+  <si>
+    <t>Digital marketing</t>
+  </si>
+  <si>
+    <t>Frontend development (html and CSS)</t>
+  </si>
+  <si>
+    <t>UI/UX development</t>
+  </si>
+  <si>
+    <t>Web development and fundamentals</t>
+  </si>
+  <si>
+    <t>Java programming</t>
+  </si>
+  <si>
+    <t>26T-B-UID</t>
+  </si>
+  <si>
+    <t>Elevate</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -485,8 +686,18 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF434343"/>
+      <name val="Roboto"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Roboto"/>
+    </font>
   </fonts>
-  <fills count="35">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -678,8 +889,20 @@
         <bgColor rgb="FFF8F9FA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8F9FA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="11">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -809,6 +1032,28 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -854,7 +1099,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -868,14 +1113,32 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="35" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="36" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="35" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1232,7 +1495,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EC2C977-6593-425B-AEB9-E3A7F18DC4A2}">
-  <dimension ref="B1:AB34"/>
+  <dimension ref="B1:AB64"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.26953125" customWidth="1"/>
@@ -1620,10 +1883,10 @@
       <c r="E21" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="F21" s="7" t="s">
+      <c r="F21" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="G21" s="7" t="s">
+      <c r="G21" s="3" t="s">
         <v>55</v>
       </c>
     </row>
@@ -1640,10 +1903,10 @@
       <c r="E22" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="F22" s="7" t="s">
+      <c r="F22" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="G22" s="7" t="s">
+      <c r="G22" s="3" t="s">
         <v>55</v>
       </c>
     </row>
@@ -1660,10 +1923,10 @@
       <c r="E23" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F23" s="7" t="s">
+      <c r="F23" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="G23" s="7" t="s">
+      <c r="G23" s="3" t="s">
         <v>55</v>
       </c>
     </row>
@@ -1680,10 +1943,10 @@
       <c r="E24" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="F24" s="7" t="s">
+      <c r="F24" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="G24" s="7" t="s">
+      <c r="G24" s="3" t="s">
         <v>55</v>
       </c>
     </row>
@@ -1700,10 +1963,10 @@
       <c r="E25" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="F25" s="7" t="s">
+      <c r="F25" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="G25" s="7" t="s">
+      <c r="G25" s="3" t="s">
         <v>55</v>
       </c>
     </row>
@@ -1720,10 +1983,10 @@
       <c r="E26" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="F26" s="7" t="s">
+      <c r="F26" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="G26" s="7" t="s">
+      <c r="G26" s="3" t="s">
         <v>55</v>
       </c>
     </row>
@@ -1740,10 +2003,10 @@
       <c r="E27" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="F27" s="7" t="s">
+      <c r="F27" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="G27" s="7" t="s">
+      <c r="G27" s="3" t="s">
         <v>55</v>
       </c>
     </row>
@@ -1760,10 +2023,10 @@
       <c r="E28" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F28" s="7" t="s">
+      <c r="F28" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="G28" s="7" t="s">
+      <c r="G28" s="3" t="s">
         <v>55</v>
       </c>
     </row>
@@ -1780,10 +2043,10 @@
       <c r="E29" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="F29" s="7" t="s">
+      <c r="F29" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="G29" s="7" t="s">
+      <c r="G29" s="3" t="s">
         <v>55</v>
       </c>
     </row>
@@ -1800,10 +2063,10 @@
       <c r="E30" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="F30" s="7" t="s">
+      <c r="F30" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="G30" s="7" t="s">
+      <c r="G30" s="3" t="s">
         <v>55</v>
       </c>
     </row>
@@ -1820,10 +2083,10 @@
       <c r="E31" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F31" s="7" t="s">
+      <c r="F31" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="G31" s="7" t="s">
+      <c r="G31" s="3" t="s">
         <v>55</v>
       </c>
     </row>
@@ -1840,10 +2103,10 @@
       <c r="E32" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="F32" s="7" t="s">
+      <c r="F32" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="G32" s="7" t="s">
+      <c r="G32" s="3" t="s">
         <v>55</v>
       </c>
     </row>
@@ -1860,32 +2123,556 @@
       <c r="E33" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="F33" s="7" t="s">
+      <c r="F33" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="G33" s="7" t="s">
+      <c r="G33" s="3" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C34" s="6" t="s">
+      <c r="C34" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="D34" s="6" t="s">
+      <c r="D34" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="E34" s="6" t="s">
+      <c r="E34" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="F34" s="7" t="s">
+      <c r="F34" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="G34" s="7" t="s">
-        <v>55</v>
-      </c>
+      <c r="G34" s="8" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B35" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="D35" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="E35" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B36" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="D36" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="E36" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="37" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B37" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="C37" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="D37" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="E37" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B38" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="D38" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="E38" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="39" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B39" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="C39" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="D39" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="E39" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="40" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B40" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="D40" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="E40" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="41" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B41" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="C41" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="D41" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="E41" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="42" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B42" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="C42" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="D42" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="E42" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="43" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B43" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="C43" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="D43" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="E43" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="44" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B44" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="C44" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="D44" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E44" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="45" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B45" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="C45" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="D45" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="E45" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="49" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B49" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="C49" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="D49" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E49" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="F49" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="G49" s="9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="50" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B50" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="C50" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="D50" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E50" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F50" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="G50" s="9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="51" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B51" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="C51" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="D51" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="E51" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="F51" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="G51" s="9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="52" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B52" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="C52" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="D52" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E52" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F52" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="G52" s="9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="53" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B53" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="C53" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="D53" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="E53" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F53" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="G53" s="9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="54" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B54" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="C54" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="D54" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="E54" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="F54" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="G54" s="9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="55" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B55" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="C55" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="D55" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="E55" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="F55" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="G55" s="9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="56" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B56" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="C56" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="D56" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="E56" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="F56" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="G56" s="9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="57" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B57" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="C57" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="D57" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E57" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="F57" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="G57" s="9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="58" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B58" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="C58" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="D58" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="E58" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="F58" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="G58" s="9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="59" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B59" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="C59" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="D59" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E59" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="F59" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="G59" s="9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="60" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B60" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="C60" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="D60" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="E60" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="F60" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="G60" s="9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="61" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B61" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="C61" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="D61" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E61" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F61" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="G61" s="9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="62" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B62" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="C62" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="D62" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="E62" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F62" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="G62" s="9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="63" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B63" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="C63" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="D63" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="E63" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="F63" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="G63" s="9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="64" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="F64" s="13"/>
+      <c r="G64" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/frontend/Premium Final Submission Form (Responses).xlsx
+++ b/frontend/Premium Final Submission Form (Responses).xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="181">
   <si>
     <t xml:space="preserve">Full Name </t>
   </si>
@@ -564,6 +564,12 @@
   </si>
   <si>
     <t>M26IP277</t>
+  </si>
+  <si>
+    <t>Harini</t>
+  </si>
+  <si>
+    <t>M26IP288</t>
   </si>
 </sst>
 </file>
@@ -576,7 +582,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -594,6 +600,12 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Roboto"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1073,55 +1085,55 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1163,6 +1175,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
@@ -1635,7 +1653,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B1:AB65"/>
+  <dimension ref="B1:AB66"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="9.27272727272727" customWidth="1"/>
@@ -2850,6 +2868,26 @@
         <v>11</v>
       </c>
     </row>
+    <row r="66" spans="2:7">
+      <c r="B66" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="C66" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="D66" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="E66" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="F66" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="G66" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
